--- a/Excel/StockQuotation (9).xlsx
+++ b/Excel/StockQuotation (9).xlsx
@@ -402,7 +402,7 @@
         <v/>
       </c>
       <c r="C1" t="str">
-        <v>03/02/23 13:00:31</v>
+        <v>07/02/23 23:30:58</v>
       </c>
     </row>
     <row r="4">
@@ -426,34 +426,34 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>169.39</v>
+        <v>167.89</v>
       </c>
       <c r="B7" t="str">
-        <v>0.57 (0.3376%)</v>
+        <v>-0.44 (-0.2613%)</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7">
-        <v>169.67</v>
+        <v>168.79</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7">
-        <v>168.43</v>
+        <v>167.57</v>
       </c>
       <c r="G7" t="str">
         <v>Volume</v>
       </c>
       <c r="H7">
-        <v>95454083</v>
+        <v>498846882</v>
       </c>
       <c r="I7" t="str">
         <v>Value</v>
       </c>
       <c r="J7">
-        <v>1271583030.51</v>
+        <v>2833516027.14</v>
       </c>
     </row>
     <row r="9">
@@ -534,22 +534,22 @@
         <v>-</v>
       </c>
       <c r="C11">
+        <v>196.5</v>
+      </c>
+      <c r="D11">
+        <v>-0.5</v>
+      </c>
+      <c r="E11">
+        <v>-0.25380710659898476</v>
+      </c>
+      <c r="F11">
+        <v>197</v>
+      </c>
+      <c r="G11">
         <v>198</v>
       </c>
-      <c r="D11">
-        <v>0.5</v>
-      </c>
-      <c r="E11">
-        <v>0.25316455696202533</v>
-      </c>
-      <c r="F11">
-        <v>197.5</v>
-      </c>
-      <c r="G11">
-        <v>198.5</v>
-      </c>
       <c r="H11">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -558,22 +558,22 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>926679</v>
+        <v>3223977</v>
       </c>
       <c r="L11">
-        <v>183244.338</v>
+        <v>633905.6665</v>
       </c>
       <c r="M11">
-        <v>127900</v>
+        <v>581100</v>
       </c>
       <c r="N11">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O11">
-        <v>198.5</v>
+        <v>196.5</v>
       </c>
       <c r="P11">
-        <v>132800</v>
+        <v>51200</v>
       </c>
     </row>
     <row r="12">
@@ -584,46 +584,46 @@
         <v>-</v>
       </c>
       <c r="C12">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="D12">
-        <v>0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="E12">
-        <v>2.255639097744361</v>
+        <v>-1.492537313432836</v>
       </c>
       <c r="F12">
         <v>6.7</v>
       </c>
       <c r="G12">
-        <v>6.85</v>
+        <v>6.7</v>
       </c>
       <c r="H12">
+        <v>6.6</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1178324</v>
+      </c>
+      <c r="L12">
+        <v>7806.0696</v>
+      </c>
+      <c r="M12">
+        <v>594500</v>
+      </c>
+      <c r="N12">
+        <v>6.6</v>
+      </c>
+      <c r="O12">
         <v>6.65</v>
       </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>3994938</v>
-      </c>
-      <c r="L12">
-        <v>26984.162399999997</v>
-      </c>
-      <c r="M12">
-        <v>30300</v>
-      </c>
-      <c r="N12">
-        <v>6.75</v>
-      </c>
-      <c r="O12">
-        <v>6.8</v>
-      </c>
       <c r="P12">
-        <v>851100</v>
+        <v>337700</v>
       </c>
     </row>
     <row r="13">
@@ -634,13 +634,13 @@
         <v>-</v>
       </c>
       <c r="C13">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="D13">
         <v>0.02</v>
       </c>
       <c r="E13">
-        <v>0.8849557522123894</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="F13">
         <v>2.26</v>
@@ -649,31 +649,31 @@
         <v>2.28</v>
       </c>
       <c r="H13">
+        <v>2.24</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>1413000</v>
+      </c>
+      <c r="L13">
+        <v>3204.234</v>
+      </c>
+      <c r="M13">
+        <v>400600</v>
+      </c>
+      <c r="N13">
+        <v>2.24</v>
+      </c>
+      <c r="O13">
         <v>2.26</v>
       </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>22500</v>
-      </c>
-      <c r="L13">
-        <v>50.852</v>
-      </c>
-      <c r="M13">
-        <v>26300</v>
-      </c>
-      <c r="N13">
-        <v>2.26</v>
-      </c>
-      <c r="O13">
-        <v>2.28</v>
-      </c>
       <c r="P13">
-        <v>93300</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="14">
@@ -684,13 +684,13 @@
         <v>-</v>
       </c>
       <c r="C14">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>1.015228426395939</v>
       </c>
       <c r="F14">
         <v>3.94</v>
@@ -708,22 +708,22 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>63400</v>
+        <v>866100</v>
       </c>
       <c r="L14">
-        <v>250.904</v>
+        <v>3428.01</v>
       </c>
       <c r="M14">
-        <v>40600</v>
+        <v>101000</v>
       </c>
       <c r="N14">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="O14">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="P14">
-        <v>28800</v>
+        <v>36100</v>
       </c>
     </row>
     <row r="15">
@@ -784,16 +784,16 @@
         <v>-</v>
       </c>
       <c r="C16">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="D16">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>0.7352941176470589</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="G16">
         <v>13.7</v>
@@ -808,13 +808,13 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>2027115</v>
+        <v>7390171</v>
       </c>
       <c r="L16">
-        <v>27759.6015</v>
+        <v>100849.8838</v>
       </c>
       <c r="M16">
-        <v>17751900</v>
+        <v>14955500</v>
       </c>
       <c r="N16">
         <v>13.6</v>
@@ -823,7 +823,7 @@
         <v>13.7</v>
       </c>
       <c r="P16">
-        <v>6676200</v>
+        <v>14400800</v>
       </c>
     </row>
     <row r="17">
@@ -834,46 +834,46 @@
         <v>-</v>
       </c>
       <c r="C17">
-        <v>50</v>
+        <v>49.75</v>
       </c>
       <c r="D17">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>0.5025125628140703</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>50</v>
+        <v>49.75</v>
       </c>
       <c r="G17">
         <v>50</v>
       </c>
       <c r="H17">
+        <v>49.25</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>3615781</v>
+      </c>
+      <c r="L17">
+        <v>179304.867</v>
+      </c>
+      <c r="M17">
+        <v>419300</v>
+      </c>
+      <c r="N17">
+        <v>49.5</v>
+      </c>
+      <c r="O17">
         <v>49.75</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>1996532</v>
-      </c>
-      <c r="L17">
-        <v>99501.42075</v>
-      </c>
-      <c r="M17">
-        <v>244600</v>
-      </c>
-      <c r="N17">
-        <v>49.75</v>
-      </c>
-      <c r="O17">
-        <v>50</v>
-      </c>
       <c r="P17">
-        <v>715600</v>
+        <v>54800</v>
       </c>
     </row>
     <row r="18">
@@ -884,46 +884,46 @@
         <v>-</v>
       </c>
       <c r="C18">
+        <v>2.24</v>
+      </c>
+      <c r="D18">
+        <v>-0.02</v>
+      </c>
+      <c r="E18">
+        <v>-0.8849557522123894</v>
+      </c>
+      <c r="F18">
+        <v>2.26</v>
+      </c>
+      <c r="G18">
+        <v>2.26</v>
+      </c>
+      <c r="H18">
+        <v>2.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>5864314</v>
+      </c>
+      <c r="L18">
+        <v>13036.87</v>
+      </c>
+      <c r="M18">
+        <v>210100</v>
+      </c>
+      <c r="N18">
         <v>2.22</v>
       </c>
-      <c r="D18">
-        <v>0.06</v>
-      </c>
-      <c r="E18">
-        <v>2.7777777777777777</v>
-      </c>
-      <c r="F18">
-        <v>2.18</v>
-      </c>
-      <c r="G18">
+      <c r="O18">
         <v>2.24</v>
       </c>
-      <c r="H18">
-        <v>2.16</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>5542921</v>
-      </c>
-      <c r="L18">
-        <v>12234.64622</v>
-      </c>
-      <c r="M18">
-        <v>786200</v>
-      </c>
-      <c r="N18">
-        <v>2.2</v>
-      </c>
-      <c r="O18">
-        <v>2.22</v>
-      </c>
       <c r="P18">
-        <v>143400</v>
+        <v>204800</v>
       </c>
     </row>
     <row r="19">
@@ -934,22 +934,22 @@
         <v>-</v>
       </c>
       <c r="C19">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D19">
-        <v>0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="E19">
-        <v>0.5586592178770949</v>
+        <v>-1.1764705882352942</v>
       </c>
       <c r="F19">
-        <v>45.25</v>
+        <v>43</v>
       </c>
       <c r="G19">
-        <v>45.5</v>
+        <v>43.25</v>
       </c>
       <c r="H19">
-        <v>43.5</v>
+        <v>41.75</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -958,22 +958,22 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>2782771</v>
+        <v>3803210</v>
       </c>
       <c r="L19">
-        <v>123323.04675</v>
+        <v>160872.318</v>
       </c>
       <c r="M19">
-        <v>72800</v>
+        <v>104300</v>
       </c>
       <c r="N19">
-        <v>44.75</v>
+        <v>42</v>
       </c>
       <c r="O19">
-        <v>45</v>
+        <v>42.25</v>
       </c>
       <c r="P19">
-        <v>134600</v>
+        <v>87400</v>
       </c>
     </row>
     <row r="20">
@@ -987,43 +987,43 @@
         <v>12.6</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>1.6129032258064515</v>
       </c>
       <c r="F20">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="G20">
         <v>12.7</v>
       </c>
       <c r="H20">
+        <v>12.3</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>5246533</v>
+      </c>
+      <c r="L20">
+        <v>65452.071200000006</v>
+      </c>
+      <c r="M20">
+        <v>8000</v>
+      </c>
+      <c r="N20">
+        <v>12.5</v>
+      </c>
+      <c r="O20">
         <v>12.6</v>
       </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>676635</v>
-      </c>
-      <c r="L20">
-        <v>8532.4411</v>
-      </c>
-      <c r="M20">
-        <v>90600</v>
-      </c>
-      <c r="N20">
-        <v>12.6</v>
-      </c>
-      <c r="O20">
-        <v>12.7</v>
-      </c>
       <c r="P20">
-        <v>186800</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="21">
@@ -1034,7 +1034,7 @@
         <v>-</v>
       </c>
       <c r="C21">
-        <v>7.35</v>
+        <v>7.8</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>7.4</v>
+        <v>7.85</v>
       </c>
       <c r="G21">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="H21">
-        <v>7.3</v>
+        <v>7.75</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1058,22 +1058,22 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>409222</v>
+        <v>3641118</v>
       </c>
       <c r="L21">
-        <v>3012.86275</v>
+        <v>28484.72065</v>
       </c>
       <c r="M21">
-        <v>258900</v>
+        <v>180600</v>
       </c>
       <c r="N21">
-        <v>7.3</v>
+        <v>7.75</v>
       </c>
       <c r="O21">
-        <v>7.35</v>
+        <v>7.8</v>
       </c>
       <c r="P21">
-        <v>97300</v>
+        <v>79700</v>
       </c>
     </row>
     <row r="22">
@@ -1084,22 +1084,22 @@
         <v>-</v>
       </c>
       <c r="C22">
-        <v>5.5</v>
+        <v>5.65</v>
       </c>
       <c r="D22">
         <v>0.15</v>
       </c>
       <c r="E22">
-        <v>2.803738317757009</v>
+        <v>2.727272727272727</v>
       </c>
       <c r="F22">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G22">
-        <v>5.5</v>
+        <v>6.05</v>
       </c>
       <c r="H22">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1108,22 +1108,22 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>890404</v>
+        <v>6313330</v>
       </c>
       <c r="L22">
-        <v>4834.8268</v>
+        <v>36021.726350000004</v>
       </c>
       <c r="M22">
-        <v>93000</v>
+        <v>22300</v>
       </c>
       <c r="N22">
-        <v>5.45</v>
+        <v>5.6</v>
       </c>
       <c r="O22">
-        <v>5.5</v>
+        <v>5.65</v>
       </c>
       <c r="P22">
-        <v>254300</v>
+        <v>74100</v>
       </c>
     </row>
     <row r="23">
@@ -1134,22 +1134,22 @@
         <v>-</v>
       </c>
       <c r="C23">
-        <v>3.42</v>
+        <v>3.78</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F23">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="G23">
-        <v>3.44</v>
+        <v>3.92</v>
       </c>
       <c r="H23">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1158,22 +1158,22 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>1543455</v>
+        <v>61098668</v>
       </c>
       <c r="L23">
-        <v>5274.1192</v>
+        <v>231570.54988</v>
       </c>
       <c r="M23">
-        <v>289600</v>
+        <v>336100</v>
       </c>
       <c r="N23">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
       <c r="O23">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="P23">
-        <v>58500</v>
+        <v>117400</v>
       </c>
     </row>
     <row r="24">
@@ -1184,46 +1184,46 @@
         <v>-</v>
       </c>
       <c r="C24">
-        <v>73.5</v>
+        <v>72.5</v>
       </c>
       <c r="D24">
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E24">
-        <v>0.684931506849315</v>
+        <v>-0.3436426116838488</v>
       </c>
       <c r="F24">
         <v>72.75</v>
       </c>
       <c r="G24">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H24">
+        <v>72.25</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>1572591</v>
+      </c>
+      <c r="L24">
+        <v>114134.26675</v>
+      </c>
+      <c r="M24">
+        <v>25400</v>
+      </c>
+      <c r="N24">
+        <v>72.5</v>
+      </c>
+      <c r="O24">
         <v>72.75</v>
       </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>802203</v>
-      </c>
-      <c r="L24">
-        <v>58812.5405</v>
-      </c>
-      <c r="M24">
-        <v>85100</v>
-      </c>
-      <c r="N24">
-        <v>73.25</v>
-      </c>
-      <c r="O24">
-        <v>73.5</v>
-      </c>
       <c r="P24">
-        <v>37400</v>
+        <v>154600</v>
       </c>
     </row>
     <row r="25">
@@ -1234,22 +1234,22 @@
         <v>-</v>
       </c>
       <c r="C25">
-        <v>3.76</v>
+        <v>4.12</v>
       </c>
       <c r="D25">
         <v>-0.02</v>
       </c>
       <c r="E25">
-        <v>-0.5291005291005291</v>
+        <v>-0.4830917874396135</v>
       </c>
       <c r="F25">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="G25">
-        <v>3.82</v>
+        <v>4.22</v>
       </c>
       <c r="H25">
-        <v>3.76</v>
+        <v>4.06</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1258,22 +1258,22 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>2472647</v>
+        <v>26726143</v>
       </c>
       <c r="L25">
-        <v>9354.12644</v>
+        <v>110904.4647</v>
       </c>
       <c r="M25">
-        <v>914200</v>
+        <v>186900</v>
       </c>
       <c r="N25">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="O25">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="P25">
-        <v>158900</v>
+        <v>146000</v>
       </c>
     </row>
     <row r="26">
@@ -1284,22 +1284,22 @@
         <v>-</v>
       </c>
       <c r="C26">
+        <v>2.36</v>
+      </c>
+      <c r="D26">
+        <v>0.04</v>
+      </c>
+      <c r="E26">
+        <v>1.7241379310344827</v>
+      </c>
+      <c r="F26">
         <v>2.34</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>2.36</v>
       </c>
       <c r="G26">
         <v>2.36</v>
       </c>
       <c r="H26">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1308,13 +1308,13 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>5064413</v>
+        <v>13297303</v>
       </c>
       <c r="L26">
-        <v>11865.426720000001</v>
+        <v>31148.86982</v>
       </c>
       <c r="M26">
-        <v>385400</v>
+        <v>1434600</v>
       </c>
       <c r="N26">
         <v>2.34</v>
@@ -1323,7 +1323,7 @@
         <v>2.36</v>
       </c>
       <c r="P26">
-        <v>4133500</v>
+        <v>3630000</v>
       </c>
     </row>
     <row r="27">
@@ -1334,7 +1334,7 @@
         <v>-</v>
       </c>
       <c r="C27">
-        <v>8.2</v>
+        <v>8.25</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1343,7 +1343,7 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>8.2</v>
+        <v>8.25</v>
       </c>
       <c r="G27">
         <v>8.25</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>1744122</v>
+        <v>3589348</v>
       </c>
       <c r="L27">
-        <v>14310.09435</v>
+        <v>29533.3456</v>
       </c>
       <c r="M27">
-        <v>3790100</v>
+        <v>5322900</v>
       </c>
       <c r="N27">
         <v>8.2</v>
@@ -1373,7 +1373,7 @@
         <v>8.25</v>
       </c>
       <c r="P27">
-        <v>5811700</v>
+        <v>4778800</v>
       </c>
     </row>
     <row r="28">
@@ -1384,22 +1384,22 @@
         <v>-</v>
       </c>
       <c r="C28">
-        <v>37.75</v>
+        <v>36.75</v>
       </c>
       <c r="D28">
-        <v>0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="E28">
-        <v>0.6666666666666666</v>
+        <v>-1.342281879194631</v>
       </c>
       <c r="F28">
-        <v>37.75</v>
+        <v>37.25</v>
       </c>
       <c r="G28">
-        <v>37.75</v>
+        <v>37.5</v>
       </c>
       <c r="H28">
-        <v>37.25</v>
+        <v>36.5</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1408,22 +1408,22 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>2354123</v>
+        <v>8468235</v>
       </c>
       <c r="L28">
-        <v>88332.3235</v>
+        <v>313643.9825</v>
       </c>
       <c r="M28">
-        <v>432200</v>
+        <v>306400</v>
       </c>
       <c r="N28">
-        <v>37.5</v>
+        <v>36.75</v>
       </c>
       <c r="O28">
-        <v>37.75</v>
+        <v>37</v>
       </c>
       <c r="P28">
-        <v>663300</v>
+        <v>181800</v>
       </c>
     </row>
     <row r="29">
@@ -1434,22 +1434,22 @@
         <v>-</v>
       </c>
       <c r="C29">
-        <v>47.5</v>
+        <v>42.75</v>
       </c>
       <c r="D29">
-        <v>-0.75</v>
+        <v>-1</v>
       </c>
       <c r="E29">
-        <v>-1.5544041450777202</v>
+        <v>-2.2857142857142856</v>
       </c>
       <c r="F29">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G29">
-        <v>48</v>
+        <v>43.5</v>
       </c>
       <c r="H29">
-        <v>47.25</v>
+        <v>41.75</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1458,22 +1458,22 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>962852</v>
+        <v>1394282</v>
       </c>
       <c r="L29">
-        <v>45923.89025</v>
+        <v>59402.07275</v>
       </c>
       <c r="M29">
-        <v>5700</v>
+        <v>24200</v>
       </c>
       <c r="N29">
-        <v>47.5</v>
+        <v>42.75</v>
       </c>
       <c r="O29">
-        <v>47.75</v>
+        <v>43</v>
       </c>
       <c r="P29">
-        <v>6900</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="30">
@@ -1484,46 +1484,46 @@
         <v>-</v>
       </c>
       <c r="C30">
-        <v>8.2</v>
+        <v>8.1</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>-0.6134969325153374</v>
       </c>
       <c r="F30">
         <v>8.2</v>
       </c>
       <c r="G30">
-        <v>8.25</v>
+        <v>8.2</v>
       </c>
       <c r="H30">
+        <v>8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>349601</v>
+      </c>
+      <c r="L30">
+        <v>2830.04815</v>
+      </c>
+      <c r="M30">
+        <v>15600</v>
+      </c>
+      <c r="N30">
+        <v>8.1</v>
+      </c>
+      <c r="O30">
         <v>8.15</v>
       </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>49514</v>
-      </c>
-      <c r="L30">
-        <v>405.1487</v>
-      </c>
-      <c r="M30">
-        <v>42800</v>
-      </c>
-      <c r="N30">
-        <v>8.15</v>
-      </c>
-      <c r="O30">
-        <v>8.2</v>
-      </c>
       <c r="P30">
-        <v>33700</v>
+        <v>17800</v>
       </c>
     </row>
     <row r="31">
@@ -1537,16 +1537,16 @@
         <v>9.6</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>-1.0309278350515463</v>
       </c>
       <c r="F31">
-        <v>9.65</v>
+        <v>9.7</v>
       </c>
       <c r="G31">
-        <v>9.65</v>
+        <v>9.7</v>
       </c>
       <c r="H31">
         <v>9.6</v>
@@ -1558,13 +1558,13 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>11200</v>
+        <v>70010</v>
       </c>
       <c r="L31">
-        <v>107.575</v>
+        <v>673.90645</v>
       </c>
       <c r="M31">
-        <v>2200</v>
+        <v>36300</v>
       </c>
       <c r="N31">
         <v>9.6</v>
@@ -1573,7 +1573,7 @@
         <v>9.65</v>
       </c>
       <c r="P31">
-        <v>4100</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="32">
@@ -1584,16 +1584,16 @@
         <v>-</v>
       </c>
       <c r="C32">
-        <v>6.85</v>
+        <v>6.9</v>
       </c>
       <c r="D32">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>-0.7246376811594203</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>6.95</v>
+        <v>6.9</v>
       </c>
       <c r="G32">
         <v>6.95</v>
@@ -1608,22 +1608,22 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>69731</v>
+        <v>90758</v>
       </c>
       <c r="L32">
-        <v>477.86854999999997</v>
+        <v>623.8628</v>
       </c>
       <c r="M32">
-        <v>118300</v>
+        <v>26900</v>
       </c>
       <c r="N32">
-        <v>6.8</v>
+        <v>6.85</v>
       </c>
       <c r="O32">
-        <v>6.85</v>
+        <v>6.9</v>
       </c>
       <c r="P32">
-        <v>10000</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="33">
@@ -1634,22 +1634,22 @@
         <v>-</v>
       </c>
       <c r="C33">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="D33">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="E33">
-        <v>0.8849557522123894</v>
+        <v>-1.7543859649122806</v>
       </c>
       <c r="F33">
-        <v>5.7</v>
+        <v>5.85</v>
       </c>
       <c r="G33">
-        <v>6</v>
+        <v>5.85</v>
       </c>
       <c r="H33">
-        <v>5.65</v>
+        <v>5.6</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -1658,22 +1658,22 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>16569929</v>
+        <v>9903903</v>
       </c>
       <c r="L33">
-        <v>96573.90879999999</v>
+        <v>56251.202</v>
       </c>
       <c r="M33">
-        <v>692300</v>
+        <v>643900</v>
       </c>
       <c r="N33">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="O33">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="P33">
-        <v>145200</v>
+        <v>1186400</v>
       </c>
     </row>
     <row r="34">
@@ -1684,19 +1684,19 @@
         <v>-</v>
       </c>
       <c r="C34">
-        <v>6.85</v>
+        <v>6.8</v>
       </c>
       <c r="D34">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E34">
-        <v>0.7352941176470589</v>
+        <v>-0.7299270072992701</v>
       </c>
       <c r="F34">
-        <v>6.85</v>
+        <v>6.95</v>
       </c>
       <c r="G34">
-        <v>7.2</v>
+        <v>6.95</v>
       </c>
       <c r="H34">
         <v>6.8</v>
@@ -1708,13 +1708,13 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>2018201</v>
+        <v>210301</v>
       </c>
       <c r="L34">
-        <v>14106.10215</v>
+        <v>1437.2718</v>
       </c>
       <c r="M34">
-        <v>157600</v>
+        <v>34900</v>
       </c>
       <c r="N34">
         <v>6.8</v>
@@ -1723,7 +1723,7 @@
         <v>6.85</v>
       </c>
       <c r="P34">
-        <v>100200</v>
+        <v>248700</v>
       </c>
     </row>
     <row r="35">
@@ -1734,22 +1734,22 @@
         <v>-</v>
       </c>
       <c r="C35">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="D35">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="E35">
-        <v>7.142857142857143</v>
+        <v>-9.090909090909092</v>
       </c>
       <c r="F35">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="G35">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="H35">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1758,22 +1758,22 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>6427305</v>
+        <v>276501167</v>
       </c>
       <c r="L35">
-        <v>946.54375</v>
+        <v>56365.44675</v>
       </c>
       <c r="M35">
-        <v>27181300</v>
+        <v>16070500</v>
       </c>
       <c r="N35">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="O35">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="P35">
-        <v>40143600</v>
+        <v>24083800</v>
       </c>
     </row>
     <row r="36">
@@ -1784,46 +1784,46 @@
         <v>-</v>
       </c>
       <c r="C36">
-        <v>27.25</v>
+        <v>27</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>0.9345794392523364</v>
       </c>
       <c r="F36">
-        <v>27.25</v>
+        <v>27</v>
       </c>
       <c r="G36">
-        <v>27.25</v>
+        <v>27</v>
       </c>
       <c r="H36">
+        <v>26.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>287202</v>
+      </c>
+      <c r="L36">
+        <v>7707.92875</v>
+      </c>
+      <c r="M36">
+        <v>48300</v>
+      </c>
+      <c r="N36">
+        <v>26.75</v>
+      </c>
+      <c r="O36">
         <v>27</v>
       </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>68701</v>
-      </c>
-      <c r="L36">
-        <v>1858.07725</v>
-      </c>
-      <c r="M36">
-        <v>27400</v>
-      </c>
-      <c r="N36">
-        <v>27</v>
-      </c>
-      <c r="O36">
-        <v>27.25</v>
-      </c>
       <c r="P36">
-        <v>37400</v>
+        <v>82600</v>
       </c>
     </row>
     <row r="37">
@@ -1834,22 +1834,22 @@
         <v>-</v>
       </c>
       <c r="C37">
-        <v>22</v>
+        <v>25.75</v>
       </c>
       <c r="D37">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E37">
-        <v>0.9174311926605505</v>
+        <v>1.9801980198019802</v>
       </c>
       <c r="F37">
-        <v>21.5</v>
+        <v>25.25</v>
       </c>
       <c r="G37">
-        <v>22.2</v>
+        <v>26</v>
       </c>
       <c r="H37">
-        <v>18.4</v>
+        <v>24.3</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -1858,22 +1858,22 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>13984692</v>
+        <v>7651251</v>
       </c>
       <c r="L37">
-        <v>291339.16760000004</v>
+        <v>192262.764</v>
       </c>
       <c r="M37">
-        <v>34000</v>
+        <v>34800</v>
       </c>
       <c r="N37">
-        <v>21.9</v>
+        <v>25.5</v>
       </c>
       <c r="O37">
-        <v>22</v>
+        <v>25.75</v>
       </c>
       <c r="P37">
-        <v>7600</v>
+        <v>84100</v>
       </c>
     </row>
     <row r="38">
@@ -1899,7 +1899,7 @@
         <v>2.62</v>
       </c>
       <c r="H38">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -1908,13 +1908,13 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>571601</v>
+        <v>593935</v>
       </c>
       <c r="L38">
-        <v>1486.0526</v>
+        <v>1539.7057</v>
       </c>
       <c r="M38">
-        <v>215600</v>
+        <v>77200</v>
       </c>
       <c r="N38">
         <v>2.58</v>
@@ -1923,7 +1923,7 @@
         <v>2.6</v>
       </c>
       <c r="P38">
-        <v>26900</v>
+        <v>137500</v>
       </c>
     </row>
     <row r="39">
@@ -1933,47 +1933,47 @@
       <c r="B39" t="str">
         <v>-</v>
       </c>
-      <c r="C39" t="str">
-        <v>-</v>
-      </c>
-      <c r="D39" t="str">
-        <v>-</v>
-      </c>
-      <c r="E39" t="str">
-        <v>-</v>
-      </c>
-      <c r="F39" t="str">
-        <v>-</v>
-      </c>
-      <c r="G39" t="str">
-        <v>-</v>
-      </c>
-      <c r="H39" t="str">
-        <v>-</v>
-      </c>
-      <c r="I39" t="str">
-        <v>-</v>
-      </c>
-      <c r="J39" t="str">
-        <v>-</v>
-      </c>
-      <c r="K39" t="str">
-        <v>-</v>
-      </c>
-      <c r="L39" t="str">
-        <v>-</v>
+      <c r="C39">
+        <v>6</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>6</v>
+      </c>
+      <c r="G39">
+        <v>6</v>
+      </c>
+      <c r="H39">
+        <v>5.95</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>2500</v>
+      </c>
+      <c r="L39">
+        <v>14.945</v>
       </c>
       <c r="M39">
-        <v>3300</v>
+        <v>400</v>
       </c>
       <c r="N39">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="O39">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="P39">
-        <v>1100</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="40">
@@ -1984,22 +1984,22 @@
         <v>-</v>
       </c>
       <c r="C40">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="D40">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>1.2121212121212122</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>16.4</v>
+        <v>17.2</v>
       </c>
       <c r="G40">
-        <v>16.7</v>
+        <v>17.6</v>
       </c>
       <c r="H40">
-        <v>16.4</v>
+        <v>17</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2008,22 +2008,22 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>917273</v>
+        <v>6475566</v>
       </c>
       <c r="L40">
-        <v>15234.4586</v>
+        <v>112298.1049</v>
       </c>
       <c r="M40">
-        <v>81100</v>
+        <v>9600</v>
       </c>
       <c r="N40">
-        <v>16.6</v>
+        <v>17.1</v>
       </c>
       <c r="O40">
-        <v>16.7</v>
+        <v>17.2</v>
       </c>
       <c r="P40">
-        <v>128600</v>
+        <v>203200</v>
       </c>
     </row>
     <row r="41">
@@ -2034,22 +2034,22 @@
         <v>-</v>
       </c>
       <c r="C41">
+        <v>16.1</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>16.1</v>
+      </c>
+      <c r="G41">
         <v>16.2</v>
       </c>
-      <c r="D41">
-        <v>0.1</v>
-      </c>
-      <c r="E41">
-        <v>0.6211180124223602</v>
-      </c>
-      <c r="F41">
-        <v>16.2</v>
-      </c>
-      <c r="G41">
-        <v>16.3</v>
-      </c>
       <c r="H41">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2058,13 +2058,13 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>2458468</v>
+        <v>5819119</v>
       </c>
       <c r="L41">
-        <v>39842.401600000005</v>
+        <v>93254.035</v>
       </c>
       <c r="M41">
-        <v>339400</v>
+        <v>71300</v>
       </c>
       <c r="N41">
         <v>16.1</v>
@@ -2073,7 +2073,7 @@
         <v>16.2</v>
       </c>
       <c r="P41">
-        <v>115300</v>
+        <v>308200</v>
       </c>
     </row>
     <row r="42">
@@ -2084,22 +2084,22 @@
         <v>-</v>
       </c>
       <c r="C42">
-        <v>21.6</v>
+        <v>22.7</v>
       </c>
       <c r="D42">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="E42">
-        <v>-2.262443438914027</v>
+        <v>2.2522522522522523</v>
       </c>
       <c r="F42">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="G42">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="H42">
-        <v>21.2</v>
+        <v>22</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2108,22 +2108,22 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>1227714</v>
+        <v>2985565</v>
       </c>
       <c r="L42">
-        <v>26581.2238</v>
+        <v>67133.51</v>
       </c>
       <c r="M42">
-        <v>7700</v>
+        <v>600</v>
       </c>
       <c r="N42">
-        <v>21.5</v>
+        <v>22.6</v>
       </c>
       <c r="O42">
-        <v>21.6</v>
+        <v>22.7</v>
       </c>
       <c r="P42">
-        <v>1500</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="43">
@@ -2134,46 +2134,46 @@
         <v>-</v>
       </c>
       <c r="C43">
-        <v>4.9</v>
+        <v>4.84</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>-0.411522633744856</v>
       </c>
       <c r="F43">
+        <v>4.84</v>
+      </c>
+      <c r="G43">
         <v>4.88</v>
       </c>
-      <c r="G43">
-        <v>4.9</v>
-      </c>
       <c r="H43">
+        <v>4.82</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>24359071</v>
+      </c>
+      <c r="L43">
+        <v>118051.03344</v>
+      </c>
+      <c r="M43">
+        <v>3996600</v>
+      </c>
+      <c r="N43">
+        <v>4.82</v>
+      </c>
+      <c r="O43">
         <v>4.86</v>
       </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>12051622</v>
-      </c>
-      <c r="L43">
-        <v>58664.988880000004</v>
-      </c>
-      <c r="M43">
-        <v>1655200</v>
-      </c>
-      <c r="N43">
-        <v>4.88</v>
-      </c>
-      <c r="O43">
-        <v>4.9</v>
-      </c>
       <c r="P43">
-        <v>2827900</v>
+        <v>860400</v>
       </c>
     </row>
     <row r="44">
@@ -2187,13 +2187,13 @@
         <v>0.07</v>
       </c>
       <c r="D44">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>0.08</v>
+        <v>0.07</v>
       </c>
       <c r="G44">
         <v>0.08</v>
@@ -2208,13 +2208,13 @@
         <v>0</v>
       </c>
       <c r="K44">
-        <v>4751100</v>
+        <v>4843505</v>
       </c>
       <c r="L44">
-        <v>338.19</v>
+        <v>354.4733</v>
       </c>
       <c r="M44">
-        <v>52246600</v>
+        <v>41371400</v>
       </c>
       <c r="N44">
         <v>0.07</v>
@@ -2223,7 +2223,7 @@
         <v>0.08</v>
       </c>
       <c r="P44">
-        <v>170706200</v>
+        <v>172329200</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StockQuotation (9).xlsx
+++ b/Excel/StockQuotation (9).xlsx
@@ -402,7 +402,7 @@
         <v/>
       </c>
       <c r="C1" t="str">
-        <v>07/02/23 23:30:58</v>
+        <v>08/02/23 20:06:49</v>
       </c>
     </row>
     <row r="4">
@@ -426,34 +426,34 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>167.89</v>
+        <v>166.7</v>
       </c>
       <c r="B7" t="str">
-        <v>-0.44 (-0.2613%)</v>
+        <v>-1.19 (-0.7087%)</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7">
-        <v>168.79</v>
+        <v>167.92</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7">
-        <v>167.57</v>
+        <v>166.06</v>
       </c>
       <c r="G7" t="str">
         <v>Volume</v>
       </c>
       <c r="H7">
-        <v>498846882</v>
+        <v>588179285</v>
       </c>
       <c r="I7" t="str">
         <v>Value</v>
       </c>
       <c r="J7">
-        <v>2833516027.14</v>
+        <v>3158836106.47</v>
       </c>
     </row>
     <row r="9">
@@ -534,22 +534,22 @@
         <v>-</v>
       </c>
       <c r="C11">
+        <v>195.5</v>
+      </c>
+      <c r="D11">
+        <v>-1</v>
+      </c>
+      <c r="E11">
+        <v>-0.5089058524173028</v>
+      </c>
+      <c r="F11">
+        <v>196</v>
+      </c>
+      <c r="G11">
         <v>196.5</v>
       </c>
-      <c r="D11">
-        <v>-0.5</v>
-      </c>
-      <c r="E11">
-        <v>-0.25380710659898476</v>
-      </c>
-      <c r="F11">
-        <v>197</v>
-      </c>
-      <c r="G11">
-        <v>198</v>
-      </c>
       <c r="H11">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -558,22 +558,22 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>3223977</v>
+        <v>3770659</v>
       </c>
       <c r="L11">
-        <v>633905.6665</v>
+        <v>737590.8815</v>
       </c>
       <c r="M11">
-        <v>581100</v>
+        <v>1010400</v>
       </c>
       <c r="N11">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O11">
-        <v>196.5</v>
+        <v>195.5</v>
       </c>
       <c r="P11">
-        <v>51200</v>
+        <v>235500</v>
       </c>
     </row>
     <row r="12">
@@ -584,22 +584,22 @@
         <v>-</v>
       </c>
       <c r="C12">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="D12">
         <v>-0.1</v>
       </c>
       <c r="E12">
-        <v>-1.492537313432836</v>
+        <v>-1.5151515151515151</v>
       </c>
       <c r="F12">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="G12">
-        <v>6.7</v>
+        <v>6.65</v>
       </c>
       <c r="H12">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -608,22 +608,22 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>1178324</v>
+        <v>2771756</v>
       </c>
       <c r="L12">
-        <v>7806.0696</v>
+        <v>18135.754390000002</v>
       </c>
       <c r="M12">
-        <v>594500</v>
+        <v>547000</v>
       </c>
       <c r="N12">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="O12">
-        <v>6.65</v>
+        <v>6.55</v>
       </c>
       <c r="P12">
-        <v>337700</v>
+        <v>110500</v>
       </c>
     </row>
     <row r="13">
@@ -637,13 +637,13 @@
         <v>2.26</v>
       </c>
       <c r="D13">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>0.8928571428571429</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G13">
         <v>2.28</v>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>1413000</v>
+        <v>1331100</v>
       </c>
       <c r="L13">
-        <v>3204.234</v>
+        <v>2994.226</v>
       </c>
       <c r="M13">
-        <v>400600</v>
+        <v>212600</v>
       </c>
       <c r="N13">
         <v>2.24</v>
@@ -673,7 +673,7 @@
         <v>2.26</v>
       </c>
       <c r="P13">
-        <v>14900</v>
+        <v>263200</v>
       </c>
     </row>
     <row r="14">
@@ -684,46 +684,46 @@
         <v>-</v>
       </c>
       <c r="C14">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="D14">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="E14">
-        <v>1.015228426395939</v>
+        <v>-1.0050251256281406</v>
       </c>
       <c r="F14">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="G14">
         <v>3.98</v>
       </c>
       <c r="H14">
+        <v>3.92</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>611802</v>
+      </c>
+      <c r="L14">
+        <v>2406.95592</v>
+      </c>
+      <c r="M14">
+        <v>50300</v>
+      </c>
+      <c r="N14">
+        <v>3.92</v>
+      </c>
+      <c r="O14">
         <v>3.94</v>
       </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>866100</v>
-      </c>
-      <c r="L14">
-        <v>3428.01</v>
-      </c>
-      <c r="M14">
-        <v>101000</v>
-      </c>
-      <c r="N14">
-        <v>3.96</v>
-      </c>
-      <c r="O14">
-        <v>3.98</v>
-      </c>
       <c r="P14">
-        <v>36100</v>
+        <v>19300</v>
       </c>
     </row>
     <row r="15">
@@ -784,13 +784,13 @@
         <v>-</v>
       </c>
       <c r="C16">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="F16">
         <v>13.6</v>
@@ -808,13 +808,13 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>7390171</v>
+        <v>8569954</v>
       </c>
       <c r="L16">
-        <v>100849.8838</v>
+        <v>116846.2518</v>
       </c>
       <c r="M16">
-        <v>14955500</v>
+        <v>10229700</v>
       </c>
       <c r="N16">
         <v>13.6</v>
@@ -823,7 +823,7 @@
         <v>13.7</v>
       </c>
       <c r="P16">
-        <v>14400800</v>
+        <v>16662200</v>
       </c>
     </row>
     <row r="17">
@@ -834,46 +834,46 @@
         <v>-</v>
       </c>
       <c r="C17">
-        <v>49.75</v>
+        <v>49.5</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>-0.5025125628140703</v>
       </c>
       <c r="F17">
-        <v>49.75</v>
+        <v>49.25</v>
       </c>
       <c r="G17">
-        <v>50</v>
+        <v>49.5</v>
       </c>
       <c r="H17">
+        <v>48.75</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>3575153</v>
+      </c>
+      <c r="L17">
+        <v>175856.39175</v>
+      </c>
+      <c r="M17">
+        <v>708800</v>
+      </c>
+      <c r="N17">
         <v>49.25</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>3615781</v>
-      </c>
-      <c r="L17">
-        <v>179304.867</v>
-      </c>
-      <c r="M17">
-        <v>419300</v>
-      </c>
-      <c r="N17">
+      <c r="O17">
         <v>49.5</v>
       </c>
-      <c r="O17">
-        <v>49.75</v>
-      </c>
       <c r="P17">
-        <v>54800</v>
+        <v>653000</v>
       </c>
     </row>
     <row r="18">
@@ -884,22 +884,22 @@
         <v>-</v>
       </c>
       <c r="C18">
+        <v>2.16</v>
+      </c>
+      <c r="D18">
+        <v>-0.08</v>
+      </c>
+      <c r="E18">
+        <v>-3.5714285714285716</v>
+      </c>
+      <c r="F18">
         <v>2.24</v>
       </c>
-      <c r="D18">
-        <v>-0.02</v>
-      </c>
-      <c r="E18">
-        <v>-0.8849557522123894</v>
-      </c>
-      <c r="F18">
-        <v>2.26</v>
-      </c>
       <c r="G18">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H18">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -908,22 +908,22 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>5864314</v>
+        <v>19318398</v>
       </c>
       <c r="L18">
-        <v>13036.87</v>
+        <v>41525.40252</v>
       </c>
       <c r="M18">
-        <v>210100</v>
+        <v>339600</v>
       </c>
       <c r="N18">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="O18">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="P18">
-        <v>204800</v>
+        <v>36300</v>
       </c>
     </row>
     <row r="19">
@@ -934,22 +934,22 @@
         <v>-</v>
       </c>
       <c r="C19">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D19">
-        <v>-0.5</v>
+        <v>-2</v>
       </c>
       <c r="E19">
-        <v>-1.1764705882352942</v>
+        <v>-4.761904761904762</v>
       </c>
       <c r="F19">
-        <v>43</v>
+        <v>42.25</v>
       </c>
       <c r="G19">
-        <v>43.25</v>
+        <v>43.5</v>
       </c>
       <c r="H19">
-        <v>41.75</v>
+        <v>39.5</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -958,22 +958,22 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>3803210</v>
+        <v>6595225</v>
       </c>
       <c r="L19">
-        <v>160872.318</v>
+        <v>271382.51675</v>
       </c>
       <c r="M19">
-        <v>104300</v>
+        <v>18400</v>
       </c>
       <c r="N19">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="O19">
-        <v>42.25</v>
+        <v>40.25</v>
       </c>
       <c r="P19">
-        <v>87400</v>
+        <v>154000</v>
       </c>
     </row>
     <row r="20">
@@ -984,16 +984,16 @@
         <v>-</v>
       </c>
       <c r="C20">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="D20">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E20">
-        <v>1.6129032258064515</v>
+        <v>-1.5873015873015872</v>
       </c>
       <c r="F20">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="G20">
         <v>12.7</v>
@@ -1008,22 +1008,22 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>5246533</v>
+        <v>2256720</v>
       </c>
       <c r="L20">
-        <v>65452.071200000006</v>
+        <v>28129.2783</v>
       </c>
       <c r="M20">
-        <v>8000</v>
+        <v>68100</v>
       </c>
       <c r="N20">
+        <v>12.4</v>
+      </c>
+      <c r="O20">
         <v>12.5</v>
       </c>
-      <c r="O20">
-        <v>12.6</v>
-      </c>
       <c r="P20">
-        <v>7600</v>
+        <v>127200</v>
       </c>
     </row>
     <row r="21">
@@ -1043,13 +1043,13 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>7.85</v>
+        <v>7.8</v>
       </c>
       <c r="G21">
         <v>7.9</v>
       </c>
       <c r="H21">
-        <v>7.75</v>
+        <v>7.65</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1058,22 +1058,22 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>3641118</v>
+        <v>2321143</v>
       </c>
       <c r="L21">
-        <v>28484.72065</v>
+        <v>18114.75605</v>
       </c>
       <c r="M21">
-        <v>180600</v>
+        <v>52400</v>
       </c>
       <c r="N21">
-        <v>7.75</v>
+        <v>7.8</v>
       </c>
       <c r="O21">
-        <v>7.8</v>
+        <v>7.85</v>
       </c>
       <c r="P21">
-        <v>79700</v>
+        <v>70900</v>
       </c>
     </row>
     <row r="22">
@@ -1084,23 +1084,23 @@
         <v>-</v>
       </c>
       <c r="C22">
+        <v>5.5</v>
+      </c>
+      <c r="D22">
+        <v>-0.15</v>
+      </c>
+      <c r="E22">
+        <v>-2.6548672566371683</v>
+      </c>
+      <c r="F22">
         <v>5.65</v>
       </c>
-      <c r="D22">
-        <v>0.15</v>
-      </c>
-      <c r="E22">
-        <v>2.727272727272727</v>
-      </c>
-      <c r="F22">
+      <c r="G22">
+        <v>5.65</v>
+      </c>
+      <c r="H22">
         <v>5.5</v>
       </c>
-      <c r="G22">
-        <v>6.05</v>
-      </c>
-      <c r="H22">
-        <v>5.45</v>
-      </c>
       <c r="I22">
         <v>0</v>
       </c>
@@ -1108,22 +1108,22 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>6313330</v>
+        <v>1625876</v>
       </c>
       <c r="L22">
-        <v>36021.726350000004</v>
+        <v>9060.9969</v>
       </c>
       <c r="M22">
-        <v>22300</v>
+        <v>37300</v>
       </c>
       <c r="N22">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O22">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="P22">
-        <v>74100</v>
+        <v>68800</v>
       </c>
     </row>
     <row r="23">
@@ -1134,46 +1134,46 @@
         <v>-</v>
       </c>
       <c r="C23">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="D23">
-        <v>0.18</v>
+        <v>-0.04</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>-1.0582010582010581</v>
       </c>
       <c r="F23">
+        <v>3.8</v>
+      </c>
+      <c r="G23">
+        <v>3.82</v>
+      </c>
+      <c r="H23">
+        <v>3.66</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>11737658</v>
+      </c>
+      <c r="L23">
+        <v>43883.24884</v>
+      </c>
+      <c r="M23">
+        <v>2100</v>
+      </c>
+      <c r="N23">
         <v>3.74</v>
       </c>
-      <c r="G23">
-        <v>3.92</v>
-      </c>
-      <c r="H23">
-        <v>3.64</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>61098668</v>
-      </c>
-      <c r="L23">
-        <v>231570.54988</v>
-      </c>
-      <c r="M23">
-        <v>336100</v>
-      </c>
-      <c r="N23">
-        <v>3.78</v>
-      </c>
       <c r="O23">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="P23">
-        <v>117400</v>
+        <v>259300</v>
       </c>
     </row>
     <row r="24">
@@ -1184,22 +1184,22 @@
         <v>-</v>
       </c>
       <c r="C24">
+        <v>72</v>
+      </c>
+      <c r="D24">
+        <v>-0.5</v>
+      </c>
+      <c r="E24">
+        <v>-0.6896551724137931</v>
+      </c>
+      <c r="F24">
         <v>72.5</v>
       </c>
-      <c r="D24">
-        <v>-0.25</v>
-      </c>
-      <c r="E24">
-        <v>-0.3436426116838488</v>
-      </c>
-      <c r="F24">
+      <c r="G24">
         <v>72.75</v>
       </c>
-      <c r="G24">
-        <v>73</v>
-      </c>
       <c r="H24">
-        <v>72.25</v>
+        <v>71.5</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1208,22 +1208,22 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>1572591</v>
+        <v>3001482</v>
       </c>
       <c r="L24">
-        <v>114134.26675</v>
+        <v>215776.429</v>
       </c>
       <c r="M24">
-        <v>25400</v>
+        <v>136700</v>
       </c>
       <c r="N24">
-        <v>72.5</v>
+        <v>71.75</v>
       </c>
       <c r="O24">
-        <v>72.75</v>
+        <v>72</v>
       </c>
       <c r="P24">
-        <v>154600</v>
+        <v>63900</v>
       </c>
     </row>
     <row r="25">
@@ -1234,46 +1234,46 @@
         <v>-</v>
       </c>
       <c r="C25">
+        <v>4.08</v>
+      </c>
+      <c r="D25">
+        <v>-0.04</v>
+      </c>
+      <c r="E25">
+        <v>-0.970873786407767</v>
+      </c>
+      <c r="F25">
         <v>4.12</v>
       </c>
-      <c r="D25">
-        <v>-0.02</v>
-      </c>
-      <c r="E25">
-        <v>-0.4830917874396135</v>
-      </c>
-      <c r="F25">
-        <v>4.2</v>
-      </c>
       <c r="G25">
-        <v>4.22</v>
+        <v>4.12</v>
       </c>
       <c r="H25">
+        <v>4.04</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>5315361</v>
+      </c>
+      <c r="L25">
+        <v>21669.274920000003</v>
+      </c>
+      <c r="M25">
+        <v>35700</v>
+      </c>
+      <c r="N25">
         <v>4.06</v>
       </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>26726143</v>
-      </c>
-      <c r="L25">
-        <v>110904.4647</v>
-      </c>
-      <c r="M25">
-        <v>186900</v>
-      </c>
-      <c r="N25">
-        <v>4.1</v>
-      </c>
       <c r="O25">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="P25">
-        <v>146000</v>
+        <v>270100</v>
       </c>
     </row>
     <row r="26">
@@ -1284,46 +1284,46 @@
         <v>-</v>
       </c>
       <c r="C26">
+        <v>2.3</v>
+      </c>
+      <c r="D26">
+        <v>-0.06</v>
+      </c>
+      <c r="E26">
+        <v>-2.542372881355932</v>
+      </c>
+      <c r="F26">
         <v>2.36</v>
-      </c>
-      <c r="D26">
-        <v>0.04</v>
-      </c>
-      <c r="E26">
-        <v>1.7241379310344827</v>
-      </c>
-      <c r="F26">
-        <v>2.34</v>
       </c>
       <c r="G26">
         <v>2.36</v>
       </c>
       <c r="H26">
+        <v>2.3</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>18390070</v>
+      </c>
+      <c r="L26">
+        <v>42821.61496</v>
+      </c>
+      <c r="M26">
+        <v>2709500</v>
+      </c>
+      <c r="N26">
+        <v>2.3</v>
+      </c>
+      <c r="O26">
         <v>2.32</v>
       </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>13297303</v>
-      </c>
-      <c r="L26">
-        <v>31148.86982</v>
-      </c>
-      <c r="M26">
-        <v>1434600</v>
-      </c>
-      <c r="N26">
-        <v>2.34</v>
-      </c>
-      <c r="O26">
-        <v>2.36</v>
-      </c>
       <c r="P26">
-        <v>3630000</v>
+        <v>665500</v>
       </c>
     </row>
     <row r="27">
@@ -1343,7 +1343,7 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>8.25</v>
+        <v>8.2</v>
       </c>
       <c r="G27">
         <v>8.25</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>3589348</v>
+        <v>2378027</v>
       </c>
       <c r="L27">
-        <v>29533.3456</v>
+        <v>19521.7054</v>
       </c>
       <c r="M27">
-        <v>5322900</v>
+        <v>6067000</v>
       </c>
       <c r="N27">
         <v>8.2</v>
@@ -1373,7 +1373,7 @@
         <v>8.25</v>
       </c>
       <c r="P27">
-        <v>4778800</v>
+        <v>8491800</v>
       </c>
     </row>
     <row r="28">
@@ -1384,46 +1384,46 @@
         <v>-</v>
       </c>
       <c r="C28">
-        <v>36.75</v>
+        <v>35.5</v>
       </c>
       <c r="D28">
-        <v>-0.5</v>
+        <v>-1.25</v>
       </c>
       <c r="E28">
-        <v>-1.342281879194631</v>
+        <v>-3.401360544217687</v>
       </c>
       <c r="F28">
-        <v>37.25</v>
+        <v>37</v>
       </c>
       <c r="G28">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="H28">
-        <v>36.5</v>
+        <v>35.5</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>273600</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>9712.8</v>
       </c>
       <c r="K28">
-        <v>8468235</v>
+        <v>9325750</v>
       </c>
       <c r="L28">
-        <v>313643.9825</v>
+        <v>335508.38625</v>
       </c>
       <c r="M28">
-        <v>306400</v>
+        <v>402400</v>
       </c>
       <c r="N28">
-        <v>36.75</v>
+        <v>35.5</v>
       </c>
       <c r="O28">
-        <v>37</v>
+        <v>35.75</v>
       </c>
       <c r="P28">
-        <v>181800</v>
+        <v>611600</v>
       </c>
     </row>
     <row r="29">
@@ -1434,46 +1434,46 @@
         <v>-</v>
       </c>
       <c r="C29">
-        <v>42.75</v>
+        <v>41.5</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>-1.25</v>
       </c>
       <c r="E29">
-        <v>-2.2857142857142856</v>
+        <v>-2.9239766081871346</v>
       </c>
       <c r="F29">
         <v>43</v>
       </c>
       <c r="G29">
-        <v>43.5</v>
+        <v>44.5</v>
       </c>
       <c r="H29">
+        <v>41.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>1718439</v>
+      </c>
+      <c r="L29">
+        <v>73240.58975</v>
+      </c>
+      <c r="M29">
+        <v>37500</v>
+      </c>
+      <c r="N29">
+        <v>41.5</v>
+      </c>
+      <c r="O29">
         <v>41.75</v>
       </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>1394282</v>
-      </c>
-      <c r="L29">
-        <v>59402.07275</v>
-      </c>
-      <c r="M29">
-        <v>24200</v>
-      </c>
-      <c r="N29">
-        <v>42.75</v>
-      </c>
-      <c r="O29">
-        <v>43</v>
-      </c>
       <c r="P29">
-        <v>3000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30">
@@ -1484,13 +1484,13 @@
         <v>-</v>
       </c>
       <c r="C30">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="D30">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="E30">
-        <v>-0.6134969325153374</v>
+        <v>-1.2345679012345678</v>
       </c>
       <c r="F30">
         <v>8.2</v>
@@ -1508,22 +1508,22 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>349601</v>
+        <v>395414</v>
       </c>
       <c r="L30">
-        <v>2830.04815</v>
+        <v>3190.77365</v>
       </c>
       <c r="M30">
-        <v>15600</v>
+        <v>191200</v>
       </c>
       <c r="N30">
+        <v>8</v>
+      </c>
+      <c r="O30">
         <v>8.1</v>
       </c>
-      <c r="O30">
-        <v>8.15</v>
-      </c>
       <c r="P30">
-        <v>17800</v>
+        <v>8300</v>
       </c>
     </row>
     <row r="31">
@@ -1537,43 +1537,43 @@
         <v>9.6</v>
       </c>
       <c r="D31">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>-1.0309278350515463</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>9.7</v>
+        <v>9.6</v>
       </c>
       <c r="G31">
-        <v>9.7</v>
+        <v>9.65</v>
       </c>
       <c r="H31">
+        <v>9.55</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>44003</v>
+      </c>
+      <c r="L31">
+        <v>421.96395</v>
+      </c>
+      <c r="M31">
+        <v>1800</v>
+      </c>
+      <c r="N31">
+        <v>9.55</v>
+      </c>
+      <c r="O31">
         <v>9.6</v>
       </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>70010</v>
-      </c>
-      <c r="L31">
-        <v>673.90645</v>
-      </c>
-      <c r="M31">
-        <v>36300</v>
-      </c>
-      <c r="N31">
-        <v>9.6</v>
-      </c>
-      <c r="O31">
-        <v>9.65</v>
-      </c>
       <c r="P31">
-        <v>1500</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="32">
@@ -1584,19 +1584,19 @@
         <v>-</v>
       </c>
       <c r="C32">
+        <v>6.8</v>
+      </c>
+      <c r="D32">
+        <v>-0.1</v>
+      </c>
+      <c r="E32">
+        <v>-1.4492753623188406</v>
+      </c>
+      <c r="F32">
+        <v>6.85</v>
+      </c>
+      <c r="G32">
         <v>6.9</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>6.9</v>
-      </c>
-      <c r="G32">
-        <v>6.95</v>
       </c>
       <c r="H32">
         <v>6.8</v>
@@ -1608,22 +1608,22 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>90758</v>
+        <v>208083</v>
       </c>
       <c r="L32">
-        <v>623.8628</v>
+        <v>1421.4738</v>
       </c>
       <c r="M32">
-        <v>26900</v>
+        <v>130400</v>
       </c>
       <c r="N32">
+        <v>6.8</v>
+      </c>
+      <c r="O32">
         <v>6.85</v>
       </c>
-      <c r="O32">
-        <v>6.9</v>
-      </c>
       <c r="P32">
-        <v>23200</v>
+        <v>9700</v>
       </c>
     </row>
     <row r="33">
@@ -1634,22 +1634,22 @@
         <v>-</v>
       </c>
       <c r="C33">
+        <v>5.1</v>
+      </c>
+      <c r="D33">
+        <v>-0.5</v>
+      </c>
+      <c r="E33">
+        <v>-8.928571428571429</v>
+      </c>
+      <c r="F33">
         <v>5.6</v>
       </c>
-      <c r="D33">
-        <v>-0.1</v>
-      </c>
-      <c r="E33">
-        <v>-1.7543859649122806</v>
-      </c>
-      <c r="F33">
-        <v>5.85</v>
-      </c>
       <c r="G33">
-        <v>5.85</v>
+        <v>5.6</v>
       </c>
       <c r="H33">
-        <v>5.6</v>
+        <v>5.05</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -1658,22 +1658,22 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>9903903</v>
+        <v>21403547</v>
       </c>
       <c r="L33">
-        <v>56251.202</v>
+        <v>113434.0209</v>
       </c>
       <c r="M33">
-        <v>643900</v>
+        <v>816700</v>
       </c>
       <c r="N33">
-        <v>5.55</v>
+        <v>5.1</v>
       </c>
       <c r="O33">
-        <v>5.6</v>
+        <v>5.15</v>
       </c>
       <c r="P33">
-        <v>1186400</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="34">
@@ -1684,22 +1684,22 @@
         <v>-</v>
       </c>
       <c r="C34">
+        <v>6.4</v>
+      </c>
+      <c r="D34">
+        <v>-0.4</v>
+      </c>
+      <c r="E34">
+        <v>-5.882352941176471</v>
+      </c>
+      <c r="F34">
         <v>6.8</v>
       </c>
-      <c r="D34">
-        <v>-0.05</v>
-      </c>
-      <c r="E34">
-        <v>-0.7299270072992701</v>
-      </c>
-      <c r="F34">
-        <v>6.95</v>
-      </c>
       <c r="G34">
-        <v>6.95</v>
+        <v>6.8</v>
       </c>
       <c r="H34">
-        <v>6.8</v>
+        <v>6.35</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -1708,22 +1708,22 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>210301</v>
+        <v>1445605</v>
       </c>
       <c r="L34">
-        <v>1437.2718</v>
+        <v>9487.983</v>
       </c>
       <c r="M34">
-        <v>34900</v>
+        <v>15500</v>
       </c>
       <c r="N34">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="O34">
-        <v>6.85</v>
+        <v>6.45</v>
       </c>
       <c r="P34">
-        <v>248700</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="35">
@@ -1734,46 +1734,46 @@
         <v>-</v>
       </c>
       <c r="C35">
+        <v>0.19</v>
+      </c>
+      <c r="D35">
+        <v>-0.01</v>
+      </c>
+      <c r="E35">
+        <v>-5</v>
+      </c>
+      <c r="F35">
         <v>0.2</v>
       </c>
-      <c r="D35">
-        <v>-0.02</v>
-      </c>
-      <c r="E35">
-        <v>-9.090909090909092</v>
-      </c>
-      <c r="F35">
+      <c r="G35">
         <v>0.21</v>
       </c>
-      <c r="G35">
-        <v>0.22</v>
-      </c>
       <c r="H35">
+        <v>0.17</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>377595295</v>
+      </c>
+      <c r="L35">
+        <v>70292.38670999999</v>
+      </c>
+      <c r="M35">
+        <v>18108700</v>
+      </c>
+      <c r="N35">
+        <v>0.18</v>
+      </c>
+      <c r="O35">
         <v>0.19</v>
       </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>276501167</v>
-      </c>
-      <c r="L35">
-        <v>56365.44675</v>
-      </c>
-      <c r="M35">
-        <v>16070500</v>
-      </c>
-      <c r="N35">
-        <v>0.2</v>
-      </c>
-      <c r="O35">
-        <v>0.21</v>
-      </c>
       <c r="P35">
-        <v>24083800</v>
+        <v>29577500</v>
       </c>
     </row>
     <row r="36">
@@ -1784,22 +1784,22 @@
         <v>-</v>
       </c>
       <c r="C36">
-        <v>27</v>
+        <v>26.25</v>
       </c>
       <c r="D36">
-        <v>0.25</v>
+        <v>-0.75</v>
       </c>
       <c r="E36">
-        <v>0.9345794392523364</v>
+        <v>-2.7777777777777777</v>
       </c>
       <c r="F36">
-        <v>27</v>
+        <v>27.25</v>
       </c>
       <c r="G36">
-        <v>27</v>
+        <v>27.25</v>
       </c>
       <c r="H36">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -1808,22 +1808,22 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>287202</v>
+        <v>744492</v>
       </c>
       <c r="L36">
-        <v>7707.92875</v>
+        <v>19626.482</v>
       </c>
       <c r="M36">
-        <v>48300</v>
+        <v>158600</v>
       </c>
       <c r="N36">
-        <v>26.75</v>
+        <v>26</v>
       </c>
       <c r="O36">
-        <v>27</v>
+        <v>26.25</v>
       </c>
       <c r="P36">
-        <v>82600</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="37">
@@ -1834,22 +1834,22 @@
         <v>-</v>
       </c>
       <c r="C37">
+        <v>26.5</v>
+      </c>
+      <c r="D37">
+        <v>0.75</v>
+      </c>
+      <c r="E37">
+        <v>2.912621359223301</v>
+      </c>
+      <c r="F37">
         <v>25.75</v>
       </c>
-      <c r="D37">
-        <v>0.5</v>
-      </c>
-      <c r="E37">
-        <v>1.9801980198019802</v>
-      </c>
-      <c r="F37">
-        <v>25.25</v>
-      </c>
       <c r="G37">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="H37">
-        <v>24.3</v>
+        <v>24.9</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -1858,22 +1858,22 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>7651251</v>
+        <v>10258192</v>
       </c>
       <c r="L37">
-        <v>192262.764</v>
+        <v>261849.63265</v>
       </c>
       <c r="M37">
-        <v>34800</v>
+        <v>100</v>
       </c>
       <c r="N37">
-        <v>25.5</v>
+        <v>26.25</v>
       </c>
       <c r="O37">
-        <v>25.75</v>
+        <v>26.5</v>
       </c>
       <c r="P37">
-        <v>84100</v>
+        <v>398000</v>
       </c>
     </row>
     <row r="38">
@@ -1884,22 +1884,22 @@
         <v>-</v>
       </c>
       <c r="C38">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>2.3076923076923075</v>
       </c>
       <c r="F38">
         <v>2.6</v>
       </c>
       <c r="G38">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="H38">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -1908,22 +1908,22 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>593935</v>
+        <v>10339122</v>
       </c>
       <c r="L38">
-        <v>1539.7057</v>
+        <v>27878.9526</v>
       </c>
       <c r="M38">
-        <v>77200</v>
+        <v>217000</v>
       </c>
       <c r="N38">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O38">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="P38">
-        <v>137500</v>
+        <v>80600</v>
       </c>
     </row>
     <row r="39">
@@ -1949,31 +1949,31 @@
         <v>6</v>
       </c>
       <c r="H39">
+        <v>6</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>3661</v>
+      </c>
+      <c r="L39">
+        <v>21.96295</v>
+      </c>
+      <c r="M39">
+        <v>200</v>
+      </c>
+      <c r="N39">
         <v>5.95</v>
       </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39">
-        <v>2500</v>
-      </c>
-      <c r="L39">
-        <v>14.945</v>
-      </c>
-      <c r="M39">
-        <v>400</v>
-      </c>
-      <c r="N39">
+      <c r="O39">
         <v>6</v>
       </c>
-      <c r="O39">
-        <v>6.05</v>
-      </c>
       <c r="P39">
-        <v>1200</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="40">
@@ -1984,22 +1984,22 @@
         <v>-</v>
       </c>
       <c r="C40">
+        <v>16.3</v>
+      </c>
+      <c r="D40">
+        <v>-0.8</v>
+      </c>
+      <c r="E40">
+        <v>-4.678362573099415</v>
+      </c>
+      <c r="F40">
         <v>17.1</v>
       </c>
-      <c r="D40">
-        <v>0</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40">
+      <c r="G40">
         <v>17.2</v>
       </c>
-      <c r="G40">
-        <v>17.6</v>
-      </c>
       <c r="H40">
-        <v>17</v>
+        <v>16.3</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2008,22 +2008,22 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>6475566</v>
+        <v>3347661</v>
       </c>
       <c r="L40">
-        <v>112298.1049</v>
+        <v>56075.0762</v>
       </c>
       <c r="M40">
-        <v>9600</v>
+        <v>278600</v>
       </c>
       <c r="N40">
-        <v>17.1</v>
+        <v>16.3</v>
       </c>
       <c r="O40">
-        <v>17.2</v>
+        <v>16.4</v>
       </c>
       <c r="P40">
-        <v>203200</v>
+        <v>16100</v>
       </c>
     </row>
     <row r="41">
@@ -2034,46 +2034,46 @@
         <v>-</v>
       </c>
       <c r="C41">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>0.6211180124223602</v>
       </c>
       <c r="F41">
         <v>16.1</v>
       </c>
       <c r="G41">
+        <v>16.6</v>
+      </c>
+      <c r="H41">
+        <v>16</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>11447811</v>
+      </c>
+      <c r="L41">
+        <v>186660.108</v>
+      </c>
+      <c r="M41">
+        <v>233300</v>
+      </c>
+      <c r="N41">
         <v>16.2</v>
       </c>
-      <c r="H41">
-        <v>15.9</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <v>5819119</v>
-      </c>
-      <c r="L41">
-        <v>93254.035</v>
-      </c>
-      <c r="M41">
-        <v>71300</v>
-      </c>
-      <c r="N41">
-        <v>16.1</v>
-      </c>
       <c r="O41">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P41">
-        <v>308200</v>
+        <v>56300</v>
       </c>
     </row>
     <row r="42">
@@ -2084,22 +2084,22 @@
         <v>-</v>
       </c>
       <c r="C42">
-        <v>22.7</v>
+        <v>22.4</v>
       </c>
       <c r="D42">
-        <v>0.5</v>
+        <v>-0.3</v>
       </c>
       <c r="E42">
-        <v>2.2522522522522523</v>
+        <v>-1.3215859030837005</v>
       </c>
       <c r="F42">
-        <v>22.2</v>
+        <v>22.8</v>
       </c>
       <c r="G42">
-        <v>22.9</v>
+        <v>23.2</v>
       </c>
       <c r="H42">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2108,22 +2108,22 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>2985565</v>
+        <v>2641636</v>
       </c>
       <c r="L42">
-        <v>67133.51</v>
+        <v>59639.3338</v>
       </c>
       <c r="M42">
-        <v>600</v>
+        <v>8700</v>
       </c>
       <c r="N42">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="O42">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="P42">
-        <v>8000</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="43">
@@ -2137,19 +2137,19 @@
         <v>4.84</v>
       </c>
       <c r="D43">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <v>-0.411522633744856</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>4.84</v>
+        <v>4.8</v>
       </c>
       <c r="G43">
-        <v>4.88</v>
+        <v>4.86</v>
       </c>
       <c r="H43">
-        <v>4.82</v>
+        <v>4.76</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2158,22 +2158,22 @@
         <v>0</v>
       </c>
       <c r="K43">
-        <v>24359071</v>
+        <v>36134690</v>
       </c>
       <c r="L43">
-        <v>118051.03344</v>
+        <v>173829.68425999998</v>
       </c>
       <c r="M43">
-        <v>3996600</v>
+        <v>918400</v>
       </c>
       <c r="N43">
         <v>4.82</v>
       </c>
       <c r="O43">
-        <v>4.86</v>
+        <v>4.84</v>
       </c>
       <c r="P43">
-        <v>860400</v>
+        <v>2066000</v>
       </c>
     </row>
     <row r="44">
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
       <c r="G44">
         <v>0.08</v>
@@ -2208,13 +2208,13 @@
         <v>0</v>
       </c>
       <c r="K44">
-        <v>4843505</v>
+        <v>7555500</v>
       </c>
       <c r="L44">
-        <v>354.4733</v>
+        <v>541.611</v>
       </c>
       <c r="M44">
-        <v>41371400</v>
+        <v>24956100</v>
       </c>
       <c r="N44">
         <v>0.07</v>
@@ -2223,7 +2223,7 @@
         <v>0.08</v>
       </c>
       <c r="P44">
-        <v>172329200</v>
+        <v>173086200</v>
       </c>
     </row>
   </sheetData>
